--- a/main/all-profiles.xlsx
+++ b/main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-12</t>
+    <t>2026-02-05</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright 2020-2025 Unabhängige Treuhandstelle der Universitätsmedizin Greifswald</t>
+    <t>Copyright 2020-2026 Unabhängige Treuhandstelle der Universitätsmedizin Greifswald</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/main/all-profiles.xlsx
+++ b/main/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2025.2.0</t>
+    <t>2026.1.0</t>
   </si>
   <si>
     <t>Name</t>
